--- a/dummy_daten/TAK_Touren.xlsx
+++ b/dummy_daten/TAK_Touren.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pl/git/github/PhilippLemke/DAV360_Transformator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pl/git/github/PhilippLemke/DAV360_Transformator/dummy_daten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68787889-5347-CF4E-8BBD-4F8EC8F1A0ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6ED708A-59BE-6547-BB8C-39A433DEE55A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1540" yWindow="12420" windowWidth="53720" windowHeight="18620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-11880" yWindow="11680" windowWidth="60160" windowHeight="18620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Id</t>
   </si>
@@ -149,6 +149,12 @@
   </si>
   <si>
     <t>Max Mustermann</t>
+  </si>
+  <si>
+    <t>Gruppen</t>
+  </si>
+  <si>
+    <t>Sonntagswanderung</t>
   </si>
 </sst>
 </file>
@@ -184,16 +190,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="17">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
@@ -256,10 +266,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:V2" totalsRowShown="0">
-  <autoFilter ref="A1:V2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W2" totalsRowShown="0">
+  <autoFilter ref="A1:W2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="23">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="id"/>
@@ -281,35 +291,35 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="E-Mail" dataDxfId="14">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="E-Mail" dataDxfId="15">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responder"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="13">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="14">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responderName"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Bezeichnung/Titel" dataDxfId="12">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Bezeichnung/Titel" dataDxfId="13">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rc349c2a0f6be49918a7e1af9977dd9e9"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Kategorie" dataDxfId="11">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Kategorie" dataDxfId="12">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="ra0604451a32c4ddfba47094aad2d68c4"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Beschreibung" dataDxfId="10">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Beschreibung" dataDxfId="11">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5035d437499440ce8aed5c3384fce3b3"/>
@@ -330,56 +340,56 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Gebirgsgruppe/Region" dataDxfId="9">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Gebirgsgruppe/Region" dataDxfId="10">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5763ca75742a44a19e119e1fd5608255"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Ausgangsort" dataDxfId="8">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Ausgangsort" dataDxfId="9">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rfc9748b873e046d388f16f81c6fa2d6e"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Tourenleitung/Organisation" dataDxfId="7">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Tourenleitung/Organisation" dataDxfId="8">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5fadff64815d433bbcf081f6968fa297"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Tourenart" dataDxfId="6">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Tourenart" dataDxfId="7">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r163ddab2d7a34270a07cb0e76e88c68e"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Klassifizierung" dataDxfId="5">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Klassifizierung" dataDxfId="6">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rd3a0ba4ec14f475480a8ec42b007794e"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Schwierigkeit" dataDxfId="4">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Schwierigkeit" dataDxfId="5">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rc08809efe0bc4b7aa244492c145fcff1"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Kondition" dataDxfId="3">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Kondition" dataDxfId="4">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r7fb009e6f8d945e58f0abbbea0c0d1f1"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="max. Zahl der Teilnehmenden" dataDxfId="2">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="max. Zahl der Teilnehmenden" dataDxfId="3">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rd4e7225ff967488dbaa02eb153fcb038"/>
@@ -393,20 +403,21 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Anfahrt km" dataDxfId="1">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Anfahrt km" dataDxfId="2">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r01cee705e19546c3b3d1574163ec3fb2"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Öffentliche Anreise" dataDxfId="0">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Öffentliche Anreise" dataDxfId="1">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r549fef56df1249aea248c059e48cab6e"/>
         </ext>
       </extLst>
     </tableColumn>
+    <tableColumn id="23" xr3:uid="{CCEE19F1-EDD9-8E44-AA90-D59276FF9A29}" name="Gruppen" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -736,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -745,7 +756,7 @@
     <col min="23" max="23" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -812,8 +823,11 @@
       <c r="V1" t="s">
         <v>20</v>
       </c>
+      <c r="W1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -879,6 +893,9 @@
       </c>
       <c r="V2" t="s">
         <v>33</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
